--- a/projects.xlsx
+++ b/projects.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiekw\AppData\Local\Packages\Claude_pzs8sxrjxfjjc\LocalCache\Roaming\Claude\local-agent-mode-sessions\4066490f-b14b-4277-9e03-4d3e5a78fcbd\72481438-58aa-4271-9cda-640ea750cf05\local_bed32a39-bd44-4d90-a202-85fd1479fcc9\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCE6EE3-AF06-413C-B654-446B86D865C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76618AB9-1065-4C07-8BBE-EA6CC43F5E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="3330" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="30">
   <si>
     <t>Category</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=oi2QgPH61JM</t>
+  </si>
+  <si>
+    <t>Screenshot 2026-08-22 175001.png</t>
   </si>
 </sst>
 </file>
@@ -183,7 +186,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -192,6 +195,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -495,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -535,6 +539,9 @@
       <c r="D2" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="E2" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -549,6 +556,9 @@
       <c r="D3" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="E3" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -563,6 +573,9 @@
       <c r="D4" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="E4" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -577,6 +590,9 @@
       <c r="D5" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="E5" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -591,6 +607,9 @@
       <c r="D6" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="E6" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -605,6 +624,9 @@
       <c r="D7" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="E7" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -619,6 +641,9 @@
       <c r="D8" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="E8" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -633,6 +658,9 @@
       <c r="D9" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="E9" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -647,6 +675,9 @@
       <c r="D10" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="E10" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -661,6 +692,9 @@
       <c r="D11" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="E11" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -675,6 +709,9 @@
       <c r="D12" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="E12" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -689,6 +726,9 @@
       <c r="D13" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="E13" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -703,9 +743,9 @@
       <c r="D14" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D15" s="3"/>
+      <c r="E14" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/projects.xlsx
+++ b/projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiekw\AppData\Local\Packages\Claude_pzs8sxrjxfjjc\LocalCache\Roaming\Claude\local-agent-mode-sessions\4066490f-b14b-4277-9e03-4d3e5a78fcbd\72481438-58aa-4271-9cda-640ea750cf05\local_bed32a39-bd44-4d90-a202-85fd1479fcc9\outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiekw\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD0DDA6-EDFC-41B8-893F-C153036513C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB99F0D-C9B7-426E-8EA7-46914B86EF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="33">
   <si>
     <t>Category</t>
   </si>
@@ -507,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -577,7 +577,7 @@
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -617,7 +617,7 @@
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -637,7 +637,7 @@
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -657,7 +657,7 @@
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
@@ -677,7 +677,7 @@
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -697,7 +697,7 @@
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
@@ -717,7 +717,7 @@
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
@@ -757,7 +757,7 @@
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
         <v>7</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
@@ -797,7 +797,7 @@
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
@@ -817,41 +817,62 @@
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>23</v>
       </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="D12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="D13" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="D14" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="D15" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="D16" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="D3" r:id="rId14" xr:uid="{53B9F5AA-2353-4443-89A3-47EEEB083FA5}"/>
-    <hyperlink ref="D5" r:id="rId15" xr:uid="{6F4411D5-DAEC-42BA-A8CD-E903F29DFE34}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D7" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D8" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D10" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D11" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D12" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="D13" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="D14" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="D15" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="D16" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="D17" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="D4" r:id="rId14" xr:uid="{53B9F5AA-2353-4443-89A3-47EEEB083FA5}"/>
+    <hyperlink ref="D6" r:id="rId15" xr:uid="{6F4411D5-DAEC-42BA-A8CD-E903F29DFE34}"/>
+    <hyperlink ref="D3" r:id="rId16" xr:uid="{F3629273-61C4-4A81-8FB2-83E78A5A030F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
